--- a/Employee_Reports_wi52/Lani Fernando Kachchakaduge Q0207.xlsx
+++ b/Employee_Reports_wi52/Lani Fernando Kachchakaduge Q0207.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1157,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1206,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1354,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1452,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-366</v>
+        <v>-374</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1489,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-366</v>
+        <v>-374</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1538,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1587,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1636,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1685,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1734,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1771,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1786,41 +1795,41 @@
       <c r="K28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1857,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1872,41 +1881,41 @@
       <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>20-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>20-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2060,7 +2069,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2164,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2184,7 +2193,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2213,7 +2222,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2242,7 +2251,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2271,7 +2280,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2309,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2329,7 +2338,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2358,7 +2367,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2396,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2416,7 +2425,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2445,7 +2454,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2483,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2503,7 +2512,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2532,7 +2541,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2570,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2590,7 +2599,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2628,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2648,7 +2657,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2677,7 +2686,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2706,7 +2715,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2744,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2764,7 +2773,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
